--- a/artfynd/A 45686-2025 artfynd.xlsx
+++ b/artfynd/A 45686-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83234092</v>
+        <v>80511718</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>218</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Calicium quercinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535254.0953719161</v>
+        <v>535246</v>
       </c>
       <c r="R2" t="n">
-        <v>6426976.07947919</v>
+        <v>6426970</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +741,14 @@
           <t>Kisa</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>AA3CDF0A-2E63-4443-BDC0-CD4BA8A18161</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,79 +757,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83234098</v>
+        <v>100720899</v>
       </c>
       <c r="B3" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Turner) Th.Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535280.326725615</v>
+        <v>535569</v>
       </c>
       <c r="R3" t="n">
-        <v>6426953.509631875</v>
+        <v>6427138</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,29 +842,14 @@
           <t>Kisa</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>D33E8F13-678A-43E4-ADE6-B51826BD7D9C</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,79 +858,74 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83234082</v>
+        <v>80511705</v>
       </c>
       <c r="B4" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>655</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535260.8703017738</v>
+        <v>535246</v>
       </c>
       <c r="R4" t="n">
-        <v>6426990.986580154</v>
+        <v>6426970</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,29 +947,14 @@
           <t>Kisa</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>E72F3A83-A97D-4488-8268-49632F8461F7</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,79 +963,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83234079</v>
+        <v>95831492</v>
       </c>
       <c r="B5" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223246</v>
+        <v>655</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535277.9022275405</v>
+        <v>535252</v>
       </c>
       <c r="R5" t="n">
-        <v>6426987.425082062</v>
+        <v>6426941</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,29 +1048,14 @@
           <t>Kisa</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>E8AB210C-97E1-4987-9E66-29268B38483E</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,79 +1064,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83234087</v>
+        <v>101107176</v>
       </c>
       <c r="B6" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223246</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535245.4975503644</v>
+        <v>535134</v>
       </c>
       <c r="R6" t="n">
-        <v>6426987.139133032</v>
+        <v>6426974</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,29 +1146,14 @@
           <t>Kisa</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>96152251-A591-4CCB-9B4B-440395DFE30F</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2000-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,73 +1168,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64606</v>
+        <v>101565632</v>
       </c>
       <c r="B7" t="n">
-        <v>54687</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206063</v>
+        <v>1855</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ål</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anguilla anguilla</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kisaån, nedströms Dammen, Ög</t>
+          <t>Föllingsö, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535536.3867511249</v>
+        <v>535504</v>
       </c>
       <c r="R7" t="n">
-        <v>6427014.637654608</v>
+        <v>6426908</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,27 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2004-08-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2004-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observatör: Per-Erik Larsson LST:s källa och kommentar: k271e</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,74 +1263,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Tommy Karlsson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53239702</v>
+        <v>101107186</v>
       </c>
       <c r="B8" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222295</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535580.9387780346</v>
+        <v>535200</v>
       </c>
       <c r="R8" t="n">
-        <v>6427380.895667579</v>
+        <v>6426899</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1347,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,73 +1363,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Betesvall</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53239696</v>
+        <v>101107187</v>
       </c>
       <c r="B9" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224416</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535580.9387780346</v>
+        <v>535127</v>
       </c>
       <c r="R9" t="n">
-        <v>6427380.895667579</v>
+        <v>6426918</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,22 +1444,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,77 +1460,64 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Betesvall</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15902452</v>
+        <v>102345818</v>
       </c>
       <c r="B10" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535522.2567796552</v>
+        <v>535244</v>
       </c>
       <c r="R10" t="n">
-        <v>6427349.091006451</v>
+        <v>6426951</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,22 +1541,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,77 +1557,71 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Grässlänt</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53239676</v>
+        <v>80511706</v>
       </c>
       <c r="B11" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535580.9387780346</v>
+        <v>535246</v>
       </c>
       <c r="R11" t="n">
-        <v>6427380.895667579</v>
+        <v>6426970</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1850,22 +1645,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fruktkroppar på flera ekar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,79 +1664,70 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Betesvall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15902507</v>
+        <v>101565641</v>
       </c>
       <c r="B12" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6471</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Kvarntorp, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535503.0519839593</v>
+        <v>535257</v>
       </c>
       <c r="R12" t="n">
-        <v>6427477.760235322</v>
+        <v>6426982</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1970,22 +1751,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,75 +1765,70 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Hagmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15902466</v>
+        <v>101565642</v>
       </c>
       <c r="B13" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223619</v>
+        <v>6471</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Kvarntorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535468.0472518735</v>
+        <v>535274</v>
       </c>
       <c r="R13" t="n">
-        <v>6427471.617158667</v>
+        <v>6426974</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2086,22 +1852,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,55 +1866,46 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Hagmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85997517</v>
+        <v>98849618</v>
       </c>
       <c r="B14" t="n">
-        <v>56599</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100124</v>
+        <v>100045</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2168,14 +1915,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2185,13 +1932,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535562.9208015716</v>
+        <v>535547</v>
       </c>
       <c r="R14" t="n">
-        <v>6427256.664207446</v>
+        <v>6427291</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2215,27 +1962,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flög skytteltrafik mellan sjö och uttorkad bäckravin.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,19 +2004,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>93722121</v>
+        <v>85997517</v>
       </c>
       <c r="B15" t="n">
-        <v>56599</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2297,14 +2034,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2314,13 +2051,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535564.2034518776</v>
+        <v>535563</v>
       </c>
       <c r="R15" t="n">
-        <v>6427410.968519955</v>
+        <v>6427257</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2344,27 +2081,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lågt, full fart norrut</t>
+          <t>Flög skytteltrafik mellan sjö och uttorkad bäckravin.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,61 +2106,56 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Pettersson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Pettersson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>93722363</v>
+        <v>93722121</v>
       </c>
       <c r="B16" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103055</v>
+        <v>100124</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2443,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535564.2034518776</v>
+        <v>535564</v>
       </c>
       <c r="R16" t="n">
-        <v>6427410.968519955</v>
+        <v>6427411</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2489,6 +2211,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lågt, full fart norrut</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,15 +2242,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94416005</v>
+        <v>64608</v>
       </c>
       <c r="B17" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102020</v>
+        <v>100127</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2553,32 +2275,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Ög</t>
+          <t>Kisaån, nedströms Dammen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535211.5085433541</v>
+        <v>535536</v>
       </c>
       <c r="R17" t="n">
-        <v>6426985.778963614</v>
+        <v>6427015</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,22 +2311,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Observatör: Per-Erik Larsson LST:s källa och kommentar: k271e Elfiske</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,68 +2330,58 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Tommy Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Via Tommy Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94696397</v>
+        <v>79739572</v>
       </c>
       <c r="B18" t="n">
-        <v>44331</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102019</v>
+        <v>101246</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -2696,20 +2390,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>funnen död</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svanbäcken, Kisa, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535570.730314992</v>
+        <v>535246</v>
       </c>
       <c r="R18" t="n">
-        <v>6427214.845623925</v>
+        <v>6426970</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2736,22 +2430,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hona, död, på rötterna av en stor, död ask.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2779,56 +2468,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95831492</v>
+        <v>102345815</v>
       </c>
       <c r="B19" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>655</v>
+        <v>102018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535252.2885419831</v>
+        <v>535199</v>
       </c>
       <c r="R19" t="n">
-        <v>6426940.005523826</v>
+        <v>6426990</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2852,22 +2533,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2876,7 +2547,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2895,15 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94162162</v>
+        <v>86468114</v>
       </c>
       <c r="B20" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,39 +2576,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221223</v>
+        <v>102019</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2951,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535094.9239366362</v>
+        <v>535075</v>
       </c>
       <c r="R20" t="n">
-        <v>6427073.305953224</v>
+        <v>6427072</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2981,27 +2635,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Återfunnen, i större antal jämfört med säsongen 2020.</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3010,7 +2649,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3029,47 +2667,55 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>93768535</v>
+        <v>94696397</v>
       </c>
       <c r="B21" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>102019</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3077,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535563.3434534208</v>
+        <v>535571</v>
       </c>
       <c r="R21" t="n">
-        <v>6427268.863156414</v>
+        <v>6427215</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3107,22 +2753,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3150,15 +2786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94018553</v>
+        <v>102345816</v>
       </c>
       <c r="B22" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,45 +2797,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220103</v>
+        <v>102019</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svanbäcken, Kisa, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535503.141494536</v>
+        <v>535199</v>
       </c>
       <c r="R22" t="n">
-        <v>6427467.687276214</v>
+        <v>6426990</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3228,22 +2851,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3252,7 +2865,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3271,58 +2883,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94019766</v>
+        <v>94416005</v>
       </c>
       <c r="B23" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanbäcken, Kisa, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535503.141494536</v>
+        <v>535212</v>
       </c>
       <c r="R23" t="n">
-        <v>6427467.687276214</v>
+        <v>6426985</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3349,22 +2965,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3392,58 +2998,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94072210</v>
+        <v>94416183</v>
       </c>
       <c r="B24" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>102020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svanbäcken, Kisa, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535503.141494536</v>
+        <v>535184</v>
       </c>
       <c r="R24" t="n">
-        <v>6427467.687276214</v>
+        <v>6426988</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3470,22 +3080,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3513,56 +3113,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>100722396</v>
+        <v>71726180</v>
       </c>
       <c r="B25" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>232272</v>
+        <v>102119</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svanbäcken, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535383.3997116272</v>
+        <v>535564</v>
       </c>
       <c r="R25" t="n">
-        <v>6427432.692198514</v>
+        <v>6427411</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3586,22 +3189,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3610,34 +3203,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100720899</v>
+        <v>93722159</v>
       </c>
       <c r="B26" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3645,40 +3232,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>311</v>
+        <v>102626</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535568.7492489603</v>
+        <v>535564</v>
       </c>
       <c r="R26" t="n">
-        <v>6427139.00411313</v>
+        <v>6427411</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3702,22 +3298,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3726,51 +3322,45 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>100739127</v>
+        <v>98849606</v>
       </c>
       <c r="B27" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102976</v>
+        <v>102952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3780,14 +3370,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3797,13 +3387,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535564.2034518776</v>
+        <v>535547</v>
       </c>
       <c r="R27" t="n">
-        <v>6427410.968519955</v>
+        <v>6427291</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3827,7 +3417,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3837,17 +3427,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Senare vid Vackra vägen, Föllingsö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3862,65 +3447,72 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Andreas Pettersson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Andreas Pettersson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101107176</v>
+        <v>100739127</v>
       </c>
       <c r="B28" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>102976</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535134.0523392847</v>
+        <v>535564</v>
       </c>
       <c r="R28" t="n">
-        <v>6426973.431430298</v>
+        <v>6427411</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3944,22 +3536,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Senare vid Vackra vägen, Föllingsö</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3974,27 +3571,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101107173</v>
+        <v>93160727</v>
       </c>
       <c r="B29" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4002,37 +3594,49 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220164</v>
+        <v>102990</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535073.5756485359</v>
+        <v>535564</v>
       </c>
       <c r="R29" t="n">
-        <v>6426902.904900876</v>
+        <v>6427411</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4056,22 +3660,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4086,27 +3690,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101107187</v>
+        <v>101107183</v>
       </c>
       <c r="B30" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4114,21 +3713,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2671</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4138,10 +3737,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535127.626482692</v>
+        <v>534828</v>
       </c>
       <c r="R30" t="n">
-        <v>6426918.757522332</v>
+        <v>6427203</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4171,19 +3770,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4210,53 +3799,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101107186</v>
+        <v>93722363</v>
       </c>
       <c r="B31" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2671</v>
+        <v>103055</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535200.0516858507</v>
+        <v>535564</v>
       </c>
       <c r="R31" t="n">
-        <v>6426899.244529777</v>
+        <v>6427411</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4280,22 +3876,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4310,68 +3906,81 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101565642</v>
+        <v>87348036</v>
       </c>
       <c r="B32" t="n">
-        <v>73700</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6471</v>
+        <v>201028</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Svanbäcken N Föllingsö, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535273.7694443049</v>
+        <v>535527</v>
       </c>
       <c r="R32" t="n">
-        <v>6426974.132048804</v>
+        <v>6427211</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4395,22 +4004,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>i gräsmark i närheten av artrik torrängsrest.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4426,27 +4040,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Gunnar Ölfvingsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Gunnar Ölfvingsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101565641</v>
+        <v>71723066</v>
       </c>
       <c r="B33" t="n">
-        <v>73700</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,40 +4063,62 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6471</v>
+        <v>201143</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535256.7000406395</v>
+        <v>535564</v>
       </c>
       <c r="R33" t="n">
-        <v>6426981.935343265</v>
+        <v>6427411</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4511,22 +4142,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4535,72 +4156,91 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102345816</v>
+        <v>71723039</v>
       </c>
       <c r="B34" t="n">
-        <v>44331</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102019</v>
+        <v>201146</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535199.7795711068</v>
+        <v>535564</v>
       </c>
       <c r="R34" t="n">
-        <v>6426990.447975405</v>
+        <v>6427411</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4624,22 +4264,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4654,49 +4284,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Andreas Pettersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102345818</v>
+        <v>102345812</v>
       </c>
       <c r="B35" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45042</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>201164</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4706,10 +4331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535244.2218781211</v>
+        <v>535199</v>
       </c>
       <c r="R35" t="n">
-        <v>6426951.069967208</v>
+        <v>6426990</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4739,19 +4364,9 @@
           <t>2022-07-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4778,53 +4393,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102345815</v>
+        <v>64606</v>
       </c>
       <c r="B36" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>55724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102018</v>
+        <v>206063</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Ål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Anguilla anguilla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Kisaån, nedströms Dammen, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535199.7795711068</v>
+        <v>535536</v>
       </c>
       <c r="R36" t="n">
-        <v>6426990.447975405</v>
+        <v>6427015</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4848,22 +4462,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Observatör: Per-Erik Larsson LST:s källa och kommentar: k271e</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4878,65 +4487,64 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Tommy Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Nina Marliden</t>
+          <t>Via Tommy Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102345812</v>
+        <v>86469904</v>
       </c>
       <c r="B37" t="n">
-        <v>44328</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>201164</v>
+        <v>219875</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535199.7795711068</v>
+        <v>535075</v>
       </c>
       <c r="R37" t="n">
-        <v>6426990.447975405</v>
+        <v>6427072</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4960,22 +4568,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5002,15 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101513498</v>
+        <v>94018553</v>
       </c>
       <c r="B38" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5035,36 +4628,28 @@
           <t>(L.) Walther</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535526.122817661</v>
+        <v>535503</v>
       </c>
       <c r="R38" t="n">
-        <v>6427451.985578585</v>
+        <v>6427468</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5088,27 +4673,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Årligt återbesök +12 plantor.</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5136,50 +4706,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101107171</v>
+        <v>101513498</v>
       </c>
       <c r="B39" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222771</v>
+        <v>220103</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>534884.2905767093</v>
+        <v>535526</v>
       </c>
       <c r="R39" t="n">
-        <v>6427102.746109889</v>
+        <v>6427452</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5206,22 +4787,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Årligt återbesök +12 plantor.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5230,6 +4806,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5248,15 +4825,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>102345810</v>
+        <v>101107173</v>
       </c>
       <c r="B40" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5264,21 +4836,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5288,10 +4860,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>535244.2218781211</v>
+        <v>535074</v>
       </c>
       <c r="R40" t="n">
-        <v>6426951.069967208</v>
+        <v>6426903</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5318,22 +4890,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5360,15 +4922,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101513494</v>
+        <v>94019766</v>
       </c>
       <c r="B41" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5394,19 +4951,27 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Svanbäcken, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>535525.0604925434</v>
+        <v>535503</v>
       </c>
       <c r="R41" t="n">
-        <v>6427451.976132613</v>
+        <v>6427468</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5430,22 +4995,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5454,6 +5009,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5472,15 +5028,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101107169</v>
+        <v>94416234</v>
       </c>
       <c r="B42" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5488,16 +5039,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5506,19 +5057,27 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+          <t>Kvarntorp, Kisa, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>535113.1434115676</v>
+        <v>535199</v>
       </c>
       <c r="R42" t="n">
-        <v>6426934.538295345</v>
+        <v>6426987</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5542,22 +5101,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5566,6 +5115,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5584,57 +5134,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101565639</v>
+        <v>101513494</v>
       </c>
       <c r="B43" t="n">
-        <v>102846</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220711</v>
+        <v>220228</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lungrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blitum bonus-henricus</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kvarntorp, Ög</t>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>535288.2249212434</v>
+        <v>535525</v>
       </c>
       <c r="R43" t="n">
-        <v>6426961.533348236</v>
+        <v>6427452</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5658,22 +5199,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5682,7 +5213,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5701,65 +5231,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116617027</v>
+        <v>101565636</v>
       </c>
       <c r="B44" t="n">
-        <v>57275</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102119</v>
+        <v>220228</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svanbäcken, Kisa, Ög</t>
+          <t>Kvarntorp, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>535564</v>
+        <v>535285</v>
       </c>
       <c r="R44" t="n">
-        <v>6427411</v>
+        <v>6426937</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5783,22 +5300,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5807,21 +5314,2731 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Andreas Pettersson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Andreas Pettersson</t>
+          <t>Nina Marliden</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>15902507</v>
+      </c>
+      <c r="B45" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>535503</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6427478</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>94072210</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>535503</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6427468</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>101107169</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>535113</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6426934</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>102345810</v>
+      </c>
+      <c r="B48" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>535244</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6426951</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>86298293</v>
+      </c>
+      <c r="B49" t="n">
+        <v>105816</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220711</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lungrot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Blitum bonus-henricus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Rchb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>535246</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6426970</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>101565638</v>
+      </c>
+      <c r="B50" t="n">
+        <v>105816</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220711</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lungrot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Blitum bonus-henricus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rchb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>535243</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6426977</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>101565639</v>
+      </c>
+      <c r="B51" t="n">
+        <v>105816</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220711</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lungrot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Blitum bonus-henricus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Rchb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>535288</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6426961</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>83234092</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>535254</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6426976</v>
+      </c>
+      <c r="S52" t="n">
+        <v>50</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>AA3CDF0A-2E63-4443-BDC0-CD4BA8A18161</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>93768535</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>535563</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6427268</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53239676</v>
+      </c>
+      <c r="B54" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>535581</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6427381</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Betesvall</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>92890043</v>
+      </c>
+      <c r="B55" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>535075</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6427072</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>86467906</v>
+      </c>
+      <c r="B56" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>535075</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6427072</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>94162162</v>
+      </c>
+      <c r="B57" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>535095</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6427073</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Återfunnen, i större antal jämfört med säsongen 2020.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>101107185</v>
+      </c>
+      <c r="B58" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>535074</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6426903</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>53239702</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>535581</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6427381</v>
+      </c>
+      <c r="S59" t="n">
+        <v>50</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Betesvall</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>101107171</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kisa, Kinda kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>534885</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6427102</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>83234079</v>
+      </c>
+      <c r="B61" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>535278</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6426987</v>
+      </c>
+      <c r="S61" t="n">
+        <v>50</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>E8AB210C-97E1-4987-9E66-29268B38483E</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>83234082</v>
+      </c>
+      <c r="B62" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>535261</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6426991</v>
+      </c>
+      <c r="S62" t="n">
+        <v>50</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>E72F3A83-A97D-4488-8268-49632F8461F7</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>83234087</v>
+      </c>
+      <c r="B63" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>535245</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6426987</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>96152251-A591-4CCB-9B4B-440395DFE30F</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>83234098</v>
+      </c>
+      <c r="B64" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>535280</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6426954</v>
+      </c>
+      <c r="S64" t="n">
+        <v>50</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D33E8F13-678A-43E4-ADE6-B51826BD7D9C</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>15902466</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>535468</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6427472</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>15902452</v>
+      </c>
+      <c r="B66" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>535522</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6427349</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Grässlänt</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>53239696</v>
+      </c>
+      <c r="B67" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>535581</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6427381</v>
+      </c>
+      <c r="S67" t="n">
+        <v>50</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Betesvall</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>93767475</v>
+      </c>
+      <c r="B68" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>535509</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6427365</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>100722396</v>
+      </c>
+      <c r="B69" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>535383</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6427433</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>93768207</v>
+      </c>
+      <c r="B70" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svanbäcken, Kisa, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>535515</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6427359</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45686-2025 artfynd.xlsx
+++ b/artfynd/A 45686-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80511718</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100720899</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80511705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95831492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101565632</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107186</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107187</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102345818</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80511706</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101565641</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1882,6 +1942,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101565642</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98849618</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85997517</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2239,6 +2314,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93722121</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2345,6 +2425,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64608</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79739572</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2562,6 +2652,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102345815</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2664,6 +2759,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86468114</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94696397</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2880,6 +2985,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102345816</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94416005</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94416183</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3218,6 +3338,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71726180</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93722159</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3456,6 +3586,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98849606</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3580,6 +3715,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100739127</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3699,6 +3839,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93160727</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3796,6 +3941,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107183</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3915,6 +4065,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93722363</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4049,6 +4204,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87348036</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4171,6 +4331,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71723066</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4293,6 +4458,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71723039</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4390,6 +4560,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102345812</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4496,6 +4671,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64606</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4597,6 +4777,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86469904</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4703,6 +4888,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94018553</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4822,6 +5012,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101513498</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4919,6 +5114,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107173</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5025,6 +5225,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94019766</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5131,6 +5336,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94416234</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5228,6 +5438,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101513494</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5330,6 +5545,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101565636</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5435,6 +5655,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15902507</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5541,6 +5766,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94072210</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5638,6 +5868,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107169</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5735,6 +5970,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102345810</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5837,6 +6077,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86298293</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5939,6 +6184,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101565638</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6041,6 +6291,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101565639</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6151,6 +6406,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83234092</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6257,6 +6517,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93768535</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6362,6 +6627,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53239676</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6468,6 +6738,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92890043</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6569,6 +6844,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86467906</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6688,6 +6968,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94162162</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6785,6 +7070,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107185</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6890,6 +7180,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53239702</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6987,6 +7282,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101107171</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7097,6 +7397,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83234079</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7207,6 +7512,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83234082</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7317,6 +7627,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83234087</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7425,6 +7740,11 @@
       <c r="AY64" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83234098</t>
         </is>
       </c>
     </row>
@@ -7528,6 +7848,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15902466</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7633,6 +7958,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15902452</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7734,6 +8064,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53239696</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7836,6 +8171,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93767475</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7937,6 +8277,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100722396</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8039,8 +8384,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93768207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>